--- a/artfynd/A 41546-2019 artfynd.xlsx
+++ b/artfynd/A 41546-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 41546-2019 artfynd.xlsx
+++ b/artfynd/A 41546-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1407,6 +1407,675 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>123528137</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57481</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lillsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>480775</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6596884</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska hackringar</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>123528026</v>
+      </c>
+      <c r="B9" t="n">
+        <v>56691</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lillsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>480618</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6596807</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>123528154</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57481</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lillsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>480741</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6596883</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>123528158</v>
+      </c>
+      <c r="B11" t="n">
+        <v>78861</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6450</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Skuggblåslav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hypogymnia vittata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lillsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>480736</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6596883</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>123528068</v>
+      </c>
+      <c r="B12" t="n">
+        <v>90931</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lillsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>480805</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6596861</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>123528002</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78861</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6450</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Skuggblåslav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hypogymnia vittata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lillsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>480686</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6596660</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41546-2019 artfynd.xlsx
+++ b/artfynd/A 41546-2019 artfynd.xlsx
@@ -1409,10 +1409,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123528026</v>
+        <v>123528068</v>
       </c>
       <c r="B8" t="n">
-        <v>56691</v>
+        <v>90948</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1425,50 +1425,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lillsjön, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480618</v>
+        <v>480805</v>
       </c>
       <c r="R8" t="n">
-        <v>6596807</v>
+        <v>6596861</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1509,6 +1496,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1527,10 +1515,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123528002</v>
+        <v>123528158</v>
       </c>
       <c r="B9" t="n">
-        <v>78861</v>
+        <v>78867</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1570,10 +1558,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480686</v>
+        <v>480736</v>
       </c>
       <c r="R9" t="n">
-        <v>6596660</v>
+        <v>6596883</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1633,10 +1621,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123528158</v>
+        <v>123528002</v>
       </c>
       <c r="B10" t="n">
-        <v>78861</v>
+        <v>78867</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1676,10 +1664,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480736</v>
+        <v>480686</v>
       </c>
       <c r="R10" t="n">
-        <v>6596883</v>
+        <v>6596660</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1742,11 +1730,11 @@
         <v>123528154</v>
       </c>
       <c r="B11" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1853,14 +1841,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123528068</v>
+        <v>123528026</v>
       </c>
       <c r="B12" t="n">
-        <v>90931</v>
+        <v>56697</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1869,37 +1857,50 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lillsjön, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480805</v>
+        <v>480618</v>
       </c>
       <c r="R12" t="n">
-        <v>6596861</v>
+        <v>6596807</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1940,7 +1941,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1962,11 +1962,11 @@
         <v>123528137</v>
       </c>
       <c r="B13" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">

--- a/artfynd/A 41546-2019 artfynd.xlsx
+++ b/artfynd/A 41546-2019 artfynd.xlsx
@@ -1409,10 +1409,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123528068</v>
+        <v>123528002</v>
       </c>
       <c r="B8" t="n">
-        <v>90948</v>
+        <v>78872</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1425,21 +1425,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>6450</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480805</v>
+        <v>480686</v>
       </c>
       <c r="R8" t="n">
-        <v>6596861</v>
+        <v>6596660</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1515,10 +1515,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123528158</v>
+        <v>123528068</v>
       </c>
       <c r="B9" t="n">
-        <v>78867</v>
+        <v>90953</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1531,21 +1531,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6450</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1558,10 +1558,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480736</v>
+        <v>480805</v>
       </c>
       <c r="R9" t="n">
-        <v>6596883</v>
+        <v>6596861</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1621,10 +1621,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123528002</v>
+        <v>123528158</v>
       </c>
       <c r="B10" t="n">
-        <v>78867</v>
+        <v>78872</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1664,10 +1664,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480686</v>
+        <v>480736</v>
       </c>
       <c r="R10" t="n">
-        <v>6596660</v>
+        <v>6596883</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1727,10 +1727,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123528154</v>
+        <v>123528026</v>
       </c>
       <c r="B11" t="n">
-        <v>57487</v>
+        <v>56700</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1739,25 +1739,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1769,20 +1769,24 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lillsjön, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480741</v>
+        <v>480618</v>
       </c>
       <c r="R11" t="n">
-        <v>6596883</v>
+        <v>6596807</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1841,10 +1845,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123528026</v>
+        <v>123528137</v>
       </c>
       <c r="B12" t="n">
-        <v>56697</v>
+        <v>57490</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1853,25 +1857,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1883,24 +1887,20 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lillsjön, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480618</v>
+        <v>480775</v>
       </c>
       <c r="R12" t="n">
-        <v>6596807</v>
+        <v>6596884</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1933,6 +1933,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska hackringar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1959,10 +1964,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123528137</v>
+        <v>123528154</v>
       </c>
       <c r="B13" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2011,10 +2016,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480775</v>
+        <v>480741</v>
       </c>
       <c r="R13" t="n">
-        <v>6596884</v>
+        <v>6596883</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2047,11 +2052,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-27</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska hackringar</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 41546-2019 artfynd.xlsx
+++ b/artfynd/A 41546-2019 artfynd.xlsx
@@ -1412,7 +1412,7 @@
         <v>123528002</v>
       </c>
       <c r="B8" t="n">
-        <v>78872</v>
+        <v>78874</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>123528068</v>
       </c>
       <c r="B9" t="n">
-        <v>90953</v>
+        <v>90955</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>123528158</v>
       </c>
       <c r="B10" t="n">
-        <v>78872</v>
+        <v>78874</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1727,10 +1727,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123528026</v>
+        <v>123528137</v>
       </c>
       <c r="B11" t="n">
-        <v>56700</v>
+        <v>57491</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1739,25 +1739,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1769,24 +1769,20 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lillsjön, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480618</v>
+        <v>480775</v>
       </c>
       <c r="R11" t="n">
-        <v>6596807</v>
+        <v>6596884</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1819,6 +1815,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska hackringar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1845,10 +1846,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123528137</v>
+        <v>123528154</v>
       </c>
       <c r="B12" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1897,10 +1898,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480775</v>
+        <v>480741</v>
       </c>
       <c r="R12" t="n">
-        <v>6596884</v>
+        <v>6596883</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1933,11 +1934,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-27</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska hackringar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1964,10 +1960,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123528154</v>
+        <v>123528026</v>
       </c>
       <c r="B13" t="n">
-        <v>57490</v>
+        <v>56700</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1976,25 +1972,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2006,20 +2002,24 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lillsjön, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480741</v>
+        <v>480618</v>
       </c>
       <c r="R13" t="n">
-        <v>6596883</v>
+        <v>6596807</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>

--- a/artfynd/A 41546-2019 artfynd.xlsx
+++ b/artfynd/A 41546-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1409,7 +1409,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123528002</v>
+        <v>123528158</v>
       </c>
       <c r="B8" t="n">
         <v>78874</v>
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480686</v>
+        <v>480736</v>
       </c>
       <c r="R8" t="n">
-        <v>6596660</v>
+        <v>6596883</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1515,10 +1515,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123528068</v>
+        <v>123528002</v>
       </c>
       <c r="B9" t="n">
-        <v>90955</v>
+        <v>78874</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1531,21 +1531,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>6450</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1558,10 +1558,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480805</v>
+        <v>480686</v>
       </c>
       <c r="R9" t="n">
-        <v>6596861</v>
+        <v>6596660</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1621,10 +1621,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123528158</v>
+        <v>123528068</v>
       </c>
       <c r="B10" t="n">
-        <v>78874</v>
+        <v>90955</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1637,21 +1637,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6450</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1664,10 +1664,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480736</v>
+        <v>480805</v>
       </c>
       <c r="R10" t="n">
-        <v>6596883</v>
+        <v>6596861</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1727,10 +1727,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123528137</v>
+        <v>123528026</v>
       </c>
       <c r="B11" t="n">
-        <v>57491</v>
+        <v>56700</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1739,25 +1739,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1769,20 +1769,24 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lillsjön, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480775</v>
+        <v>480618</v>
       </c>
       <c r="R11" t="n">
-        <v>6596884</v>
+        <v>6596807</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1815,11 +1819,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-27</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska hackringar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1846,7 +1845,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123528154</v>
+        <v>123528137</v>
       </c>
       <c r="B12" t="n">
         <v>57491</v>
@@ -1898,10 +1897,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480741</v>
+        <v>480775</v>
       </c>
       <c r="R12" t="n">
-        <v>6596883</v>
+        <v>6596884</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1934,6 +1933,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska hackringar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1960,10 +1964,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123528026</v>
+        <v>123528154</v>
       </c>
       <c r="B13" t="n">
-        <v>56700</v>
+        <v>57491</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1972,25 +1976,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2002,24 +2006,20 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lillsjön, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480618</v>
+        <v>480741</v>
       </c>
       <c r="R13" t="n">
-        <v>6596807</v>
+        <v>6596883</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2075,6 +2075,735 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>123987229</v>
+      </c>
+      <c r="B14" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>480599</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6596687</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>123986562</v>
+      </c>
+      <c r="B15" t="n">
+        <v>78433</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>353</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lillsjön, Lillsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>480717</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6596732</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>123986588</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lillsjön, Grythyttans sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>480714</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6596754</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringbarkning i levande tall.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>123986446</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lillsjön, Grythyttans sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>480739</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6596660</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringbarkning i döende tall.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>123986419</v>
+      </c>
+      <c r="B18" t="n">
+        <v>56700</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lillsjön, Grythyttans sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>480730</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6596628</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>123987264</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79406</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>480599</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6596687</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41546-2019 artfynd.xlsx
+++ b/artfynd/A 41546-2019 artfynd.xlsx
@@ -1727,10 +1727,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123528026</v>
+        <v>123528137</v>
       </c>
       <c r="B11" t="n">
-        <v>56700</v>
+        <v>57491</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1739,25 +1739,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1769,24 +1769,20 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lillsjön, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480618</v>
+        <v>480775</v>
       </c>
       <c r="R11" t="n">
-        <v>6596807</v>
+        <v>6596884</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1819,6 +1815,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska hackringar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1845,7 +1846,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123528137</v>
+        <v>123528154</v>
       </c>
       <c r="B12" t="n">
         <v>57491</v>
@@ -1897,10 +1898,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480775</v>
+        <v>480741</v>
       </c>
       <c r="R12" t="n">
-        <v>6596884</v>
+        <v>6596883</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1933,11 +1934,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-27</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska hackringar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1964,10 +1960,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123528154</v>
+        <v>123528026</v>
       </c>
       <c r="B13" t="n">
-        <v>57491</v>
+        <v>56700</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1976,25 +1972,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2006,20 +2002,24 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lillsjön, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480741</v>
+        <v>480618</v>
       </c>
       <c r="R13" t="n">
-        <v>6596883</v>
+        <v>6596807</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2078,10 +2078,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123987229</v>
+        <v>123986446</v>
       </c>
       <c r="B14" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2094,34 +2094,48 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+          <t>Lillsjön, Grythyttans sn, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>480599</v>
+        <v>480739</v>
       </c>
       <c r="R14" t="n">
-        <v>6596687</v>
+        <v>6596660</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2153,7 +2167,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2163,7 +2177,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringbarkning i döende tall.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2190,10 +2209,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123986562</v>
+        <v>123987138</v>
       </c>
       <c r="B15" t="n">
-        <v>78433</v>
+        <v>78788</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2206,34 +2225,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lillsjön, Lillsjön, Vstm</t>
+          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>480717</v>
+        <v>480599</v>
       </c>
       <c r="R15" t="n">
-        <v>6596732</v>
+        <v>6596687</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2265,7 +2284,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2275,7 +2294,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2302,10 +2321,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123986588</v>
+        <v>123987264</v>
       </c>
       <c r="B16" t="n">
-        <v>57491</v>
+        <v>79406</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2318,48 +2337,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lillsjön, Grythyttans sn, Vstm</t>
+          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480714</v>
+        <v>480599</v>
       </c>
       <c r="R16" t="n">
-        <v>6596754</v>
+        <v>6596687</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2391,7 +2396,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2401,12 +2406,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>08:01</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringbarkning i levande tall.</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2433,7 +2433,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123986446</v>
+        <v>123986588</v>
       </c>
       <c r="B17" t="n">
         <v>57491</v>
@@ -2487,10 +2487,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>480739</v>
+        <v>480714</v>
       </c>
       <c r="R17" t="n">
-        <v>6596660</v>
+        <v>6596754</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringbarkning i döende tall.</t>
+          <t>Ringbarkning i levande tall.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2564,10 +2564,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123986419</v>
+        <v>123986562</v>
       </c>
       <c r="B18" t="n">
-        <v>56700</v>
+        <v>78433</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2576,57 +2576,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lillsjön, Grythyttans sn, Vstm</t>
+          <t>Lillsjön, Lillsjön, Vstm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>480730</v>
+        <v>480717</v>
       </c>
       <c r="R18" t="n">
-        <v>6596628</v>
+        <v>6596732</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2658,7 +2639,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2668,7 +2649,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2695,10 +2676,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123987264</v>
+        <v>123986419</v>
       </c>
       <c r="B19" t="n">
-        <v>79406</v>
+        <v>56700</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2707,38 +2688,57 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+          <t>Lillsjön, Grythyttans sn, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>480599</v>
+        <v>480730</v>
       </c>
       <c r="R19" t="n">
-        <v>6596687</v>
+        <v>6596628</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 41546-2019 artfynd.xlsx
+++ b/artfynd/A 41546-2019 artfynd.xlsx
@@ -1727,10 +1727,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123528137</v>
+        <v>123528026</v>
       </c>
       <c r="B11" t="n">
-        <v>57491</v>
+        <v>56700</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1739,25 +1739,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1769,20 +1769,24 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lillsjön, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480775</v>
+        <v>480618</v>
       </c>
       <c r="R11" t="n">
-        <v>6596884</v>
+        <v>6596807</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1815,11 +1819,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-27</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska hackringar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1960,10 +1959,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123528026</v>
+        <v>123528137</v>
       </c>
       <c r="B13" t="n">
-        <v>56700</v>
+        <v>57491</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1972,25 +1971,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2002,24 +2001,20 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lillsjön, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480618</v>
+        <v>480775</v>
       </c>
       <c r="R13" t="n">
-        <v>6596807</v>
+        <v>6596884</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2052,6 +2047,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska hackringar</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 41546-2019 artfynd.xlsx
+++ b/artfynd/A 41546-2019 artfynd.xlsx
@@ -1409,10 +1409,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123528158</v>
+        <v>123528068</v>
       </c>
       <c r="B8" t="n">
-        <v>78874</v>
+        <v>90955</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1425,21 +1425,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6450</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480736</v>
+        <v>480805</v>
       </c>
       <c r="R8" t="n">
-        <v>6596883</v>
+        <v>6596861</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1621,10 +1621,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123528068</v>
+        <v>123528158</v>
       </c>
       <c r="B10" t="n">
-        <v>90955</v>
+        <v>78874</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1637,21 +1637,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>6450</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1664,10 +1664,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480805</v>
+        <v>480736</v>
       </c>
       <c r="R10" t="n">
-        <v>6596861</v>
+        <v>6596883</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1845,7 +1845,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123528154</v>
+        <v>123528137</v>
       </c>
       <c r="B12" t="n">
         <v>57491</v>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480741</v>
+        <v>480775</v>
       </c>
       <c r="R12" t="n">
-        <v>6596883</v>
+        <v>6596884</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1933,6 +1933,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska hackringar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1959,7 +1964,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123528137</v>
+        <v>123528154</v>
       </c>
       <c r="B13" t="n">
         <v>57491</v>
@@ -2011,10 +2016,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480775</v>
+        <v>480741</v>
       </c>
       <c r="R13" t="n">
-        <v>6596884</v>
+        <v>6596883</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2047,11 +2052,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-27</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska hackringar</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2078,10 +2078,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123986446</v>
+        <v>123987229</v>
       </c>
       <c r="B14" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2094,48 +2094,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lillsjön, Grythyttans sn, Vstm</t>
+          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>480739</v>
+        <v>480599</v>
       </c>
       <c r="R14" t="n">
-        <v>6596660</v>
+        <v>6596687</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2167,7 +2153,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2177,12 +2163,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringbarkning i döende tall.</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2209,10 +2190,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123987138</v>
+        <v>123986562</v>
       </c>
       <c r="B15" t="n">
-        <v>78788</v>
+        <v>78433</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2225,34 +2206,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+          <t>Lillsjön, Lillsjön, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>480599</v>
+        <v>480717</v>
       </c>
       <c r="R15" t="n">
-        <v>6596687</v>
+        <v>6596732</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2284,7 +2265,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2294,7 +2275,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2321,10 +2302,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123987264</v>
+        <v>123986446</v>
       </c>
       <c r="B16" t="n">
-        <v>79406</v>
+        <v>57491</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2337,34 +2318,48 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+          <t>Lillsjön, Grythyttans sn, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480599</v>
+        <v>480739</v>
       </c>
       <c r="R16" t="n">
-        <v>6596687</v>
+        <v>6596660</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2396,7 +2391,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2406,7 +2401,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringbarkning i döende tall.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2564,10 +2564,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123986562</v>
+        <v>123986419</v>
       </c>
       <c r="B18" t="n">
-        <v>78433</v>
+        <v>56700</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2576,38 +2576,57 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lillsjön, Lillsjön, Vstm</t>
+          <t>Lillsjön, Grythyttans sn, Vstm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>480717</v>
+        <v>480730</v>
       </c>
       <c r="R18" t="n">
-        <v>6596732</v>
+        <v>6596628</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2639,7 +2658,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2649,7 +2668,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2676,10 +2695,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123986419</v>
+        <v>123987264</v>
       </c>
       <c r="B19" t="n">
-        <v>56700</v>
+        <v>79406</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2688,57 +2707,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lillsjön, Grythyttans sn, Vstm</t>
+          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>480730</v>
+        <v>480599</v>
       </c>
       <c r="R19" t="n">
-        <v>6596628</v>
+        <v>6596687</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 41546-2019 artfynd.xlsx
+++ b/artfynd/A 41546-2019 artfynd.xlsx
@@ -1409,10 +1409,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123528068</v>
+        <v>123528158</v>
       </c>
       <c r="B8" t="n">
-        <v>90955</v>
+        <v>78874</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1425,21 +1425,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>6450</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480805</v>
+        <v>480736</v>
       </c>
       <c r="R8" t="n">
-        <v>6596861</v>
+        <v>6596883</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1621,10 +1621,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123528158</v>
+        <v>123528068</v>
       </c>
       <c r="B10" t="n">
-        <v>78874</v>
+        <v>90955</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1637,21 +1637,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6450</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1664,10 +1664,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480736</v>
+        <v>480805</v>
       </c>
       <c r="R10" t="n">
-        <v>6596883</v>
+        <v>6596861</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1727,10 +1727,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123528026</v>
+        <v>123528154</v>
       </c>
       <c r="B11" t="n">
-        <v>56700</v>
+        <v>57491</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1739,25 +1739,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1769,24 +1769,20 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lillsjön, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480618</v>
+        <v>480741</v>
       </c>
       <c r="R11" t="n">
-        <v>6596807</v>
+        <v>6596883</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1845,10 +1841,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123528137</v>
+        <v>123528026</v>
       </c>
       <c r="B12" t="n">
-        <v>57491</v>
+        <v>56700</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1857,25 +1853,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1887,20 +1883,24 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lillsjön, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480775</v>
+        <v>480618</v>
       </c>
       <c r="R12" t="n">
-        <v>6596884</v>
+        <v>6596807</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1933,11 +1933,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-27</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska hackringar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1964,7 +1959,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123528154</v>
+        <v>123528137</v>
       </c>
       <c r="B13" t="n">
         <v>57491</v>
@@ -2016,10 +2011,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480741</v>
+        <v>480775</v>
       </c>
       <c r="R13" t="n">
-        <v>6596883</v>
+        <v>6596884</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2052,6 +2047,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska hackringar</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2078,7 +2078,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123987229</v>
+        <v>123987267</v>
       </c>
       <c r="B14" t="n">
         <v>78788</v>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2302,10 +2302,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123986446</v>
+        <v>123986419</v>
       </c>
       <c r="B16" t="n">
-        <v>57491</v>
+        <v>56700</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2314,25 +2314,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2345,9 +2345,14 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2356,10 +2361,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480739</v>
+        <v>480730</v>
       </c>
       <c r="R16" t="n">
-        <v>6596660</v>
+        <v>6596628</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2391,7 +2396,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2401,12 +2406,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringbarkning i döende tall.</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2564,10 +2564,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123986419</v>
+        <v>123986446</v>
       </c>
       <c r="B18" t="n">
-        <v>56700</v>
+        <v>57491</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2576,25 +2576,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2607,14 +2607,9 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2623,10 +2618,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>480730</v>
+        <v>480739</v>
       </c>
       <c r="R18" t="n">
-        <v>6596628</v>
+        <v>6596660</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2658,7 +2653,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2668,7 +2663,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringbarkning i döende tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 41546-2019 artfynd.xlsx
+++ b/artfynd/A 41546-2019 artfynd.xlsx
@@ -2190,10 +2190,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123986562</v>
+        <v>123987264</v>
       </c>
       <c r="B15" t="n">
-        <v>78455</v>
+        <v>79428</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2206,34 +2206,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lillsjön, Lillsjön, Vstm</t>
+          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>480717</v>
+        <v>480599</v>
       </c>
       <c r="R15" t="n">
-        <v>6596732</v>
+        <v>6596687</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2265,7 +2265,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2302,10 +2302,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123987264</v>
+        <v>123986562</v>
       </c>
       <c r="B16" t="n">
-        <v>79428</v>
+        <v>78455</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2318,34 +2318,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+          <t>Lillsjön, Lillsjön, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480599</v>
+        <v>480717</v>
       </c>
       <c r="R16" t="n">
-        <v>6596687</v>
+        <v>6596732</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2377,7 +2377,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2387,7 +2387,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2414,37 +2414,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123986419</v>
+        <v>123986588</v>
       </c>
       <c r="B17" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2457,14 +2457,9 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2473,10 +2468,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>480730</v>
+        <v>480714</v>
       </c>
       <c r="R17" t="n">
-        <v>6596628</v>
+        <v>6596754</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2508,7 +2503,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2518,7 +2513,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringbarkning i levande tall.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2545,37 +2545,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123986588</v>
+        <v>123986419</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2588,9 +2588,14 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2599,10 +2604,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>480714</v>
+        <v>480730</v>
       </c>
       <c r="R18" t="n">
-        <v>6596754</v>
+        <v>6596628</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2634,7 +2639,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2644,12 +2649,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>08:01</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringbarkning i levande tall.</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 41546-2019 artfynd.xlsx
+++ b/artfynd/A 41546-2019 artfynd.xlsx
@@ -2078,7 +2078,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123987138</v>
+        <v>123987267</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2414,7 +2414,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123986588</v>
+        <v>123986446</v>
       </c>
       <c r="B17" t="n">
         <v>57513</v>
@@ -2468,10 +2468,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>480714</v>
+        <v>480739</v>
       </c>
       <c r="R17" t="n">
-        <v>6596754</v>
+        <v>6596660</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2503,7 +2503,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2513,12 +2513,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringbarkning i levande tall.</t>
+          <t>Ringbarkning i döende tall.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2676,7 +2676,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123986446</v>
+        <v>123986588</v>
       </c>
       <c r="B19" t="n">
         <v>57513</v>
@@ -2730,10 +2730,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>480739</v>
+        <v>480714</v>
       </c>
       <c r="R19" t="n">
-        <v>6596660</v>
+        <v>6596754</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringbarkning i döende tall.</t>
+          <t>Ringbarkning i levande tall.</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 41546-2019 artfynd.xlsx
+++ b/artfynd/A 41546-2019 artfynd.xlsx
@@ -2078,10 +2078,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123987267</v>
+        <v>123987264</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2094,21 +2094,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2190,10 +2190,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123987264</v>
+        <v>123987138</v>
       </c>
       <c r="B15" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2206,21 +2206,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2265,7 +2265,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 41546-2019 artfynd.xlsx
+++ b/artfynd/A 41546-2019 artfynd.xlsx
@@ -2078,10 +2078,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123987264</v>
+        <v>123987229</v>
       </c>
       <c r="B14" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2094,21 +2094,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2190,10 +2190,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123987138</v>
+        <v>123987264</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2206,21 +2206,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2265,7 +2265,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2414,37 +2414,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123986446</v>
+        <v>123986419</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2457,9 +2457,14 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2468,10 +2473,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>480739</v>
+        <v>480730</v>
       </c>
       <c r="R17" t="n">
-        <v>6596660</v>
+        <v>6596628</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2503,7 +2508,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2513,12 +2518,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringbarkning i döende tall.</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2545,37 +2545,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123986419</v>
+        <v>123986588</v>
       </c>
       <c r="B18" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2588,14 +2588,9 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2604,10 +2599,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>480730</v>
+        <v>480714</v>
       </c>
       <c r="R18" t="n">
-        <v>6596628</v>
+        <v>6596754</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2639,7 +2634,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2649,7 +2644,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringbarkning i levande tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2676,7 +2676,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123986588</v>
+        <v>123986446</v>
       </c>
       <c r="B19" t="n">
         <v>57513</v>
@@ -2730,10 +2730,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>480714</v>
+        <v>480739</v>
       </c>
       <c r="R19" t="n">
-        <v>6596754</v>
+        <v>6596660</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringbarkning i levande tall.</t>
+          <t>Ringbarkning i döende tall.</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 41546-2019 artfynd.xlsx
+++ b/artfynd/A 41546-2019 artfynd.xlsx
@@ -2078,7 +2078,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123987229</v>
+        <v>123987267</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2545,7 +2545,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123986588</v>
+        <v>123986446</v>
       </c>
       <c r="B18" t="n">
         <v>57513</v>
@@ -2599,10 +2599,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>480714</v>
+        <v>480739</v>
       </c>
       <c r="R18" t="n">
-        <v>6596754</v>
+        <v>6596660</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2634,7 +2634,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringbarkning i levande tall.</t>
+          <t>Ringbarkning i döende tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2676,7 +2676,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123986446</v>
+        <v>123986588</v>
       </c>
       <c r="B19" t="n">
         <v>57513</v>
@@ -2730,10 +2730,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>480739</v>
+        <v>480714</v>
       </c>
       <c r="R19" t="n">
-        <v>6596660</v>
+        <v>6596754</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringbarkning i döende tall.</t>
+          <t>Ringbarkning i levande tall.</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 41546-2019 artfynd.xlsx
+++ b/artfynd/A 41546-2019 artfynd.xlsx
@@ -2545,7 +2545,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123986446</v>
+        <v>123986588</v>
       </c>
       <c r="B18" t="n">
         <v>57513</v>
@@ -2599,10 +2599,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>480739</v>
+        <v>480714</v>
       </c>
       <c r="R18" t="n">
-        <v>6596660</v>
+        <v>6596754</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2634,7 +2634,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringbarkning i döende tall.</t>
+          <t>Ringbarkning i levande tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2676,7 +2676,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123986588</v>
+        <v>123986446</v>
       </c>
       <c r="B19" t="n">
         <v>57513</v>
@@ -2730,10 +2730,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>480714</v>
+        <v>480739</v>
       </c>
       <c r="R19" t="n">
-        <v>6596754</v>
+        <v>6596660</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringbarkning i levande tall.</t>
+          <t>Ringbarkning i döende tall.</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 41546-2019 artfynd.xlsx
+++ b/artfynd/A 41546-2019 artfynd.xlsx
@@ -2414,37 +2414,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123986419</v>
+        <v>123986588</v>
       </c>
       <c r="B17" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2457,14 +2457,9 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2473,10 +2468,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>480730</v>
+        <v>480714</v>
       </c>
       <c r="R17" t="n">
-        <v>6596628</v>
+        <v>6596754</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2508,7 +2503,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2518,7 +2513,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringbarkning i levande tall.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2545,37 +2545,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123986588</v>
+        <v>123986419</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2588,9 +2588,14 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2599,10 +2604,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>480714</v>
+        <v>480730</v>
       </c>
       <c r="R18" t="n">
-        <v>6596754</v>
+        <v>6596628</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2634,7 +2639,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2644,12 +2649,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>08:01</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringbarkning i levande tall.</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 41546-2019 artfynd.xlsx
+++ b/artfynd/A 41546-2019 artfynd.xlsx
@@ -2545,37 +2545,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123986419</v>
+        <v>123986446</v>
       </c>
       <c r="B18" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2588,14 +2588,9 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2604,10 +2599,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>480730</v>
+        <v>480739</v>
       </c>
       <c r="R18" t="n">
-        <v>6596628</v>
+        <v>6596660</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2639,7 +2634,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2649,7 +2644,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringbarkning i döende tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2676,37 +2676,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123986446</v>
+        <v>123986419</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2719,9 +2719,14 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2730,10 +2735,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>480739</v>
+        <v>480730</v>
       </c>
       <c r="R19" t="n">
-        <v>6596660</v>
+        <v>6596628</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2765,7 +2770,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2775,12 +2780,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringbarkning i döende tall.</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 41546-2019 artfynd.xlsx
+++ b/artfynd/A 41546-2019 artfynd.xlsx
@@ -2414,37 +2414,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123986588</v>
+        <v>123986419</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2457,9 +2457,14 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2468,10 +2473,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>480714</v>
+        <v>480730</v>
       </c>
       <c r="R17" t="n">
-        <v>6596754</v>
+        <v>6596628</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2503,7 +2508,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2513,12 +2518,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>08:01</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringbarkning i levande tall.</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2545,7 +2545,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123986446</v>
+        <v>123986588</v>
       </c>
       <c r="B18" t="n">
         <v>57513</v>
@@ -2599,10 +2599,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>480739</v>
+        <v>480714</v>
       </c>
       <c r="R18" t="n">
-        <v>6596660</v>
+        <v>6596754</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2634,7 +2634,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringbarkning i döende tall.</t>
+          <t>Ringbarkning i levande tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2676,37 +2676,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123986419</v>
+        <v>123986446</v>
       </c>
       <c r="B19" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2719,14 +2719,9 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2735,10 +2730,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>480730</v>
+        <v>480739</v>
       </c>
       <c r="R19" t="n">
-        <v>6596628</v>
+        <v>6596660</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2770,7 +2765,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2780,7 +2775,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringbarkning i döende tall.</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 41546-2019 artfynd.xlsx
+++ b/artfynd/A 41546-2019 artfynd.xlsx
@@ -2414,37 +2414,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123986419</v>
+        <v>123986446</v>
       </c>
       <c r="B17" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2457,14 +2457,9 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2473,10 +2468,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>480730</v>
+        <v>480739</v>
       </c>
       <c r="R17" t="n">
-        <v>6596628</v>
+        <v>6596660</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2508,7 +2503,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2518,7 +2513,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringbarkning i döende tall.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2676,37 +2676,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123986446</v>
+        <v>123986419</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2719,9 +2719,14 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2730,10 +2735,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>480739</v>
+        <v>480730</v>
       </c>
       <c r="R19" t="n">
-        <v>6596660</v>
+        <v>6596628</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2765,7 +2770,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2775,12 +2780,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringbarkning i döende tall.</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="AD19" t="b">
